--- a/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
+++ b/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
@@ -3129,12 +3129,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.186</t>
+          <t>14.016</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>&lt;0.001</t>
+          <t>0.003</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.571</t>
+          <t>7.754</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.051</t>
         </is>
       </c>
     </row>

--- a/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
+++ b/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5.1 (KM Post-hoc)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3168,4 +3169,475 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P-value(Unadj)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P-value(Bonferroni)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 0.0 / Low</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 1.0 / High</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1.967</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.161</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.338</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.247</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.0 / Low vs 1.0 / High</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>9.923999999999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0 / Low vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.574</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.0 / High vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>8.622</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 0.0 / Low</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.201</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 1.0 / High</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.939</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.0 / High vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.053</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0 / Low vs 1.0 / High</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.671</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.0 / Low vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.641</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LUSC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.0 / High vs 1.0 / Low</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6.165</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.013</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
+++ b/result_signature/Signature_2차_Signature_LUSC_Tables.xlsx
@@ -3235,20 +3235,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0 / High vs 0.0 / Low</t>
+          <t>&gt;65 / High vs &gt;65 / Low</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2.233</v>
+        <v>8.622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.020</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0 / High vs 1.0 / High</t>
+          <t>&gt;65 / High vs ≤65 / High</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -3305,20 +3305,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0 / High vs 1.0 / Low</t>
+          <t>&gt;65 / High vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.338</v>
+        <v>9.923999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -3340,20 +3340,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0 / Low vs 1.0 / High</t>
+          <t>&gt;65 / Low vs ≤65 / High</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9.923999999999999</v>
+        <v>1.338</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.0 / Low vs 1.0 / Low</t>
+          <t>&gt;65 / Low vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -3410,20 +3410,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.0 / High vs 1.0 / Low</t>
+          <t>≤65 / High vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.622</v>
+        <v>2.233</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.811</t>
         </is>
       </c>
     </row>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.0 / High vs 0.0 / Low</t>
+          <t>&gt;65 / High vs &gt;65 / Low</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.632</v>
+        <v>6.165</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>0.013</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.078</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0 / High vs 1.0 / High</t>
+          <t>&gt;65 / High vs ≤65 / High</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -3515,20 +3515,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.0 / High vs 1.0 / Low</t>
+          <t>&gt;65 / High vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3.75</v>
+        <v>2.528</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.671</t>
         </is>
       </c>
     </row>
@@ -3550,20 +3550,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0 / Low vs 1.0 / High</t>
+          <t>&gt;65 / Low vs ≤65 / High</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.528</v>
+        <v>3.75</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>0.317</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.0 / Low vs 1.0 / Low</t>
+          <t>&gt;65 / Low vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3620,20 +3620,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.0 / High vs 1.0 / Low</t>
+          <t>≤65 / High vs ≤65 / Low</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.165</v>
+        <v>1.632</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.201</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
